--- a/data/trans_dic/P6906-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6906-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño</t>
+          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 19,39</t>
+          <t>6,97; 19,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 35,4</t>
+          <t>14,16; 36,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,97; 35,13</t>
+          <t>9,74; 35,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 25,99</t>
+          <t>3,52; 27,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 27,36</t>
+          <t>5,24; 27,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 35,28</t>
+          <t>9,87; 37,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,81; 50,42</t>
+          <t>10,72; 53,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 33,27</t>
+          <t>6,96; 33,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 18,82</t>
+          <t>7,6; 18,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,71; 31,84</t>
+          <t>14,5; 31,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,1; 33,9</t>
+          <t>13,29; 34,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 23,82</t>
+          <t>7,56; 23,8</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,37; 29,47</t>
+          <t>19,08; 29,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,96; 32,43</t>
+          <t>19,35; 31,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,21; 24,94</t>
+          <t>14,24; 24,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 22,62</t>
+          <t>12,52; 23,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,04; 32,54</t>
+          <t>16,77; 32,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,78; 40,15</t>
+          <t>23,79; 41,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,91; 40,18</t>
+          <t>24,71; 40,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 28,09</t>
+          <t>13,95; 28,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,73; 28,65</t>
+          <t>19,34; 28,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,4; 32,14</t>
+          <t>22,77; 32,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,4; 28,77</t>
+          <t>18,78; 28,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,41; 23,79</t>
+          <t>15,28; 23,91</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,59; 46,23</t>
+          <t>23,15; 46,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,23; 48,45</t>
+          <t>20,74; 49,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,88; 56,27</t>
+          <t>29,64; 56,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,1; 41,26</t>
+          <t>17,08; 43,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,38; 33,23</t>
+          <t>13,63; 33,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,43; 46,9</t>
+          <t>19,47; 47,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,21; 47,87</t>
+          <t>23,22; 46,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,26; 44,04</t>
+          <t>27,23; 46,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,32; 37,14</t>
+          <t>21,42; 36,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,17; 42,85</t>
+          <t>22,8; 43,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,77; 48,0</t>
+          <t>30,5; 47,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,79; 40,14</t>
+          <t>25,25; 40,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,65; 26,87</t>
+          <t>18,99; 26,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,31; 31,2</t>
+          <t>21,38; 31,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,98; 28,87</t>
+          <t>19,02; 29,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,89; 24,79</t>
+          <t>14,2; 24,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,67; 27,49</t>
+          <t>16,43; 28,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,69; 36,26</t>
+          <t>23,59; 36,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,65; 39,62</t>
+          <t>25,81; 38,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,76; 30,02</t>
+          <t>18,47; 29,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,33; 25,67</t>
+          <t>19,12; 25,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,64; 31,5</t>
+          <t>23,83; 31,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,61; 31,41</t>
+          <t>23,65; 31,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 25,49</t>
+          <t>18,58; 25,88</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño</t>
+          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7241; 21575</t>
+          <t>7758; 21779</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7419; 20426</t>
+          <t>8173; 20881</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6651; 19526</t>
+          <t>5412; 19767</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1055; 7593</t>
+          <t>1027; 7917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1933; 10278</t>
+          <t>1968; 10242</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3842; 13384</t>
+          <t>3744; 14289</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1948; 9088</t>
+          <t>1932; 9674</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1493; 8314</t>
+          <t>1740; 8472</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11097; 28011</t>
+          <t>11318; 27458</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14064; 30447</t>
+          <t>13867; 29785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10377; 24951</t>
+          <t>9779; 25485</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3969; 12912</t>
+          <t>4099; 12899</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52720; 84574</t>
+          <t>54744; 85190</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44200; 71816</t>
+          <t>42864; 69223</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32590; 57215</t>
+          <t>32668; 56396</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29599; 54198</t>
+          <t>29995; 56140</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20210; 38586</t>
+          <t>19888; 37996</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29748; 52424</t>
+          <t>31070; 53685</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29785; 50045</t>
+          <t>30781; 50809</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31938; 66967</t>
+          <t>33255; 68688</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80022; 116171</t>
+          <t>78439; 115444</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78850; 113159</t>
+          <t>80148; 113974</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68658; 101817</t>
+          <t>66470; 99133</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73644; 113692</t>
+          <t>73032; 114294</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18216; 34242</t>
+          <t>17147; 34201</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9323; 22331</t>
+          <t>9559; 22942</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18980; 35749</t>
+          <t>18832; 35978</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11193; 28688</t>
+          <t>11873; 30051</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8560; 21261</t>
+          <t>8719; 21468</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8535; 21724</t>
+          <t>9020; 22066</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17109; 35287</t>
+          <t>17113; 34208</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23821; 39938</t>
+          <t>24697; 41758</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29432; 51275</t>
+          <t>29566; 50861</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20485; 39597</t>
+          <t>21069; 39849</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40852; 65874</t>
+          <t>41862; 65136</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39718; 64309</t>
+          <t>40449; 65236</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88075; 126925</t>
+          <t>89686; 126337</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69303; 101467</t>
+          <t>69536; 101114</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66128; 100606</t>
+          <t>66294; 102263</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50361; 83856</t>
+          <t>48058; 81401</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36699; 60513</t>
+          <t>36169; 62153</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50884; 77900</t>
+          <t>50686; 78378</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57639; 85697</t>
+          <t>55820; 83491</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>62869; 106274</t>
+          <t>65386; 105993</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>133854; 177728</t>
+          <t>132408; 178065</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>127674; 170148</t>
+          <t>128721; 171769</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>133355; 177427</t>
+          <t>133561; 177388</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>125181; 176510</t>
+          <t>128663; 179161</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6906-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6906-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 19,57</t>
+          <t>7,16; 20,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,16; 36,19</t>
+          <t>13,74; 36,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 35,56</t>
+          <t>11,84; 35,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 27,1</t>
+          <t>4,38; 30,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 27,26</t>
+          <t>5,25; 28,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,87; 37,67</t>
+          <t>10,33; 35,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,72; 53,67</t>
+          <t>10,93; 54,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 33,91</t>
+          <t>11,77; 36,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 18,45</t>
+          <t>7,58; 19,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,5; 31,14</t>
+          <t>14,87; 31,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,29; 34,62</t>
+          <t>14,21; 35,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 23,8</t>
+          <t>10,03; 28,89</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,08; 29,69</t>
+          <t>18,53; 29,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,35; 31,26</t>
+          <t>19,41; 31,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,24; 24,59</t>
+          <t>14,01; 25,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 23,43</t>
+          <t>13,67; 24,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,77; 32,05</t>
+          <t>16,3; 32,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,79; 41,11</t>
+          <t>23,47; 40,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,71; 40,79</t>
+          <t>24,0; 39,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,95; 28,82</t>
+          <t>20,44; 30,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,34; 28,47</t>
+          <t>19,22; 28,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,77; 32,37</t>
+          <t>23,11; 32,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,78; 28,01</t>
+          <t>19,56; 28,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,28; 23,91</t>
+          <t>18,09; 25,06</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,15; 46,17</t>
+          <t>23,26; 45,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,74; 49,78</t>
+          <t>20,07; 48,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,64; 56,63</t>
+          <t>29,82; 56,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,08; 43,22</t>
+          <t>17,88; 43,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,63; 33,55</t>
+          <t>12,41; 33,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,47; 47,64</t>
+          <t>19,14; 48,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,22; 46,41</t>
+          <t>24,2; 46,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,23; 46,04</t>
+          <t>25,72; 43,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,42; 36,84</t>
+          <t>20,87; 37,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,8; 43,12</t>
+          <t>23,24; 43,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,5; 47,46</t>
+          <t>30,68; 48,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,25; 40,72</t>
+          <t>25,26; 39,92</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,99; 26,75</t>
+          <t>18,68; 26,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,38; 31,09</t>
+          <t>21,29; 31,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,02; 29,34</t>
+          <t>19,41; 29,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,2; 24,06</t>
+          <t>15,74; 25,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,43; 28,24</t>
+          <t>16,67; 27,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,59; 36,48</t>
+          <t>23,1; 35,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,81; 38,6</t>
+          <t>26,98; 39,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 29,94</t>
+          <t>23,92; 32,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,12; 25,72</t>
+          <t>19,21; 25,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,83; 31,8</t>
+          <t>23,82; 31,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 31,41</t>
+          <t>23,68; 31,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,58; 25,88</t>
+          <t>20,97; 27,33</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>10559</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7758; 21779</t>
+          <t>7966; 22597</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8173; 20881</t>
+          <t>7931; 21148</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5412; 19767</t>
+          <t>6583; 19878</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1027; 7917</t>
+          <t>1586; 10953</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1968; 10242</t>
+          <t>1972; 10892</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3744; 14289</t>
+          <t>3920; 13547</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1932; 9674</t>
+          <t>1970; 9821</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1740; 8472</t>
+          <t>2885; 9066</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11318; 27458</t>
+          <t>11283; 28924</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13867; 29785</t>
+          <t>14220; 30449</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9779; 25485</t>
+          <t>10458; 26350</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4099; 12899</t>
+          <t>6088; 17545</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41311</t>
+          <t>50103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>53167</t>
+          <t>56074</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94478</t>
+          <t>106177</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54744; 85190</t>
+          <t>53183; 84879</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42864; 69223</t>
+          <t>42993; 69526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32668; 56396</t>
+          <t>32133; 57980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29995; 56140</t>
+          <t>36884; 67098</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19888; 37996</t>
+          <t>19328; 37960</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31070; 53685</t>
+          <t>30653; 52270</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30781; 50809</t>
+          <t>29895; 49163</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33255; 68688</t>
+          <t>45155; 68273</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78439; 115444</t>
+          <t>77941; 114933</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80148; 113974</t>
+          <t>81374; 115911</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66470; 99133</t>
+          <t>69219; 102203</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73032; 114294</t>
+          <t>88752; 122960</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19766</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>34477</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>56758</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17147; 34201</t>
+          <t>17233; 34019</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9559; 22942</t>
+          <t>9252; 22265</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18832; 35978</t>
+          <t>18941; 35797</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11873; 30051</t>
+          <t>13904; 33730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8719; 21468</t>
+          <t>7939; 21708</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9020; 22066</t>
+          <t>8868; 22257</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17113; 34208</t>
+          <t>17835; 34301</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24697; 41758</t>
+          <t>25572; 42980</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29566; 50861</t>
+          <t>28812; 51799</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21069; 39849</t>
+          <t>21475; 39788</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41862; 65136</t>
+          <t>42104; 66052</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40449; 65236</t>
+          <t>44752; 70732</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64442</t>
+          <t>77437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>89206</t>
+          <t>96056</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>153648</t>
+          <t>173494</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89686; 126337</t>
+          <t>88246; 126617</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69536; 101114</t>
+          <t>69235; 101461</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66294; 102263</t>
+          <t>67651; 101414</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48058; 81401</t>
+          <t>60398; 97279</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36169; 62153</t>
+          <t>36686; 60996</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50686; 78378</t>
+          <t>49624; 77038</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55820; 83491</t>
+          <t>58361; 85372</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65386; 105993</t>
+          <t>82460; 111544</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>132408; 178065</t>
+          <t>133037; 179563</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>128721; 171769</t>
+          <t>128662; 170528</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>133561; 177388</t>
+          <t>133755; 178488</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>128663; 179161</t>
+          <t>152751; 199085</t>
         </is>
       </c>
     </row>
